--- a/РАБОЧИЙ СТОЛ/расчет ПОКОМ КИ/дв 30,06,26 бррсч пок ки.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчет ПОКОМ КИ/дв 30,06,26 бррсч пок ки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчет ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D6E828-B10B-4CF6-8CFE-C4695FA83C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD4172F-1FA2-4F86-8F1A-C101ED353A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
